--- a/output/vino_prezzi_2026-03-27.xlsx
+++ b/output/vino_prezzi_2026-03-27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -525,12 +525,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Puglia IGT Tre di Tre 2023 Lupo Meraviglia, 6 bottiglie da 0,75 ℓ</t>
+          <t>Puglia IGT Uno di Uno Rosé 2024 Lupo Meraviglia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -539,14 +539,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59.4</v>
+        <v>10.7</v>
       </c>
       <c r="F3" t="n">
-        <v>59.4</v>
+        <v>10.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-tre-di-tre-lupo-meraviglia-2023_v.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-due-di-due-rosato-lupo-meraviglia-2024.html</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puglia IGT Uno di Uno Rosé 2024 Lupo Meraviglia</t>
+          <t>Puglia IGT Rosso Due di Due 2023 Lupo Meraviglia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,14 +582,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="F4" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-due-di-due-rosato-lupo-meraviglia-2024.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-due-di-due-lupo-meraviglia-2023.html</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Puglia IGT Rosso Due di Due 2023 Lupo Meraviglia</t>
+          <t>Puglia IGT Vermentino Uno di Uno 2025 Lupo Meraviglia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-due-di-due-lupo-meraviglia-2023.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-vermentino-uno-di-uno-lupo-meraviglia-2025.html</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puglia IGT Vermentino Uno di Uno 2025 Lupo Meraviglia</t>
+          <t>Puglia IGT Rosso Tre di Tre Limited Edition 2023 Lupo Meraviglia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.4</v>
+        <v>14.9</v>
       </c>
       <c r="F6" t="n">
-        <v>10.4</v>
+        <v>14.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-vermentino-uno-di-uno-lupo-meraviglia-2025.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-rosso-tre-di-tre-limited-edition-lupo-meraviglia-2023.html</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Puglia IGT Rosso Tre di Tre Limited Edition 2023 Lupo Meraviglia</t>
+          <t>Puglia IGT Tre di Tre 2023 Lupo Meraviglia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,18 +707,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0,75 L</t>
+          <t>Magnum 1,5 L</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9</v>
+        <v>18.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -728,24 +728,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-rosso-tre-di-tre-limited-edition-lupo-meraviglia-2023.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-tre-di-tre-magnum-lupo-meraviglia-2023.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LUPO MERAVIGLIA</t>
+          <t>GRAN PASSIONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Puglia IGT Rosso Tre di Tre Limited Edition 2023 Lupo Meraviglia, 6 bottiglie da 0,75 ℓ</t>
+          <t>Veneto IGT Rosso Gran Passione 2024 Botter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>89.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="F8" t="n">
-        <v>89.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -771,40 +771,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-rosso-tre-di-tre-limited-edition-lupo-meraviglia-2023_v.html</t>
+          <t>https://www.vino.com/dettaglio/veneto-igt-rosso-gran-passione-2024.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUPO MERAVIGLIA</t>
+          <t>GRAN PASSIONE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Puglia IGT Tre di Tre 2023 Lupo Meraviglia</t>
+          <t>Veneto IGT Bianco Gran Passione 2024 Botter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>0,75 L</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="F9" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-tre-di-tre-magnum-lupo-meraviglia-2023.html</t>
+          <t>https://www.vino.com/dettaglio/veneto-igt-bianco-gran-passione-2024.html</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Veneto IGT Rosso Gran Passione 2024 Botter</t>
+          <t>Amarone della Valpolicella DOCG Gran Passione 2019 Botter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>24.2</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>24.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -857,24 +857,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/veneto-igt-rosso-gran-passione-2024.html</t>
+          <t>https://www.vino.com/dettaglio/amarone-della-valpolicella-docg-gran-passione-botter-2019.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRAN PASSIONE</t>
+          <t>TOR DEL COLLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Veneto IGT Rosso Gran Passione 2024 Botter, 6 bottiglie da 0,75 ℓ</t>
+          <t>Biferno DOC Rosso Riserva 2019 Tor Del Colle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>44.4</v>
+        <v>7.1</v>
       </c>
       <c r="F11" t="n">
-        <v>44.4</v>
+        <v>7.1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -900,19 +900,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/veneto-igt-rosso-gran-passione-2024_v.html</t>
+          <t>https://www.vino.com/dettaglio/biferno-doc-rosso-riserva-tor-del-colle-2019.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRAN PASSIONE</t>
+          <t>TOR DEL COLLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Veneto IGT Bianco Gran Passione 2024 Botter</t>
+          <t>Terre d'Abruzzo IGT Pecorino 2024 Tor Del Colle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>7.1</v>
       </c>
       <c r="F12" t="n">
-        <v>10.9</v>
+        <v>7.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -943,24 +943,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/veneto-igt-bianco-gran-passione-2024.html</t>
+          <t>https://www.vino.com/dettaglio/terre-dabruzzo-igt-pecorino-tor-del-colle-2024.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRAN PASSIONE</t>
+          <t>TOR DEL COLLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amarone della Valpolicella DOCG Gran Passione 2019 Botter</t>
+          <t>Molise DOC Rosso Riserva 2018 Tor Del Colle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>24.2</v>
+        <v>10.5</v>
       </c>
       <c r="F13" t="n">
-        <v>24.2</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/amarone-della-valpolicella-docg-gran-passione-botter-2019.html</t>
+          <t>https://www.vino.com/dettaglio/molise-doc-rosso-riserva-tor-del-colle-2018.html</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Biferno DOC Rosso Riserva 2019 Tor Del Colle</t>
+          <t>Montepulciano d'Abruzzo DOC Riserva 2020 Tor Del Colle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1012,14 +1012,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.1</v>
+        <v>9.9</v>
       </c>
       <c r="F14" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1029,24 +1029,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/biferno-doc-rosso-riserva-tor-del-colle-2019.html</t>
+          <t>https://www.vino.com/dettaglio/montepulciano-abruzzo-doc-riserva-tor-del-colle-2020.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TOR DEL COLLE</t>
+          <t>BRILLA!</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Terre d'Abruzzo IGT Pecorino 2024 Tor Del Colle</t>
+          <t>Prosecco  DOC Extra Dry Brilla!</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1072,24 +1072,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-dabruzzo-igt-pecorino-tor-del-colle-2024.html</t>
+          <t>https://www.vino.com/dettaglio/prosecco-doc-brilla.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOR DEL COLLE</t>
+          <t>BRILLA!</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Molise DOC Rosso Riserva 2018 Tor Del Colle</t>
+          <t>Prosecco Superiore di Asolo DOCG Brut Brilla!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1115,24 +1115,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/molise-doc-rosso-riserva-tor-del-colle-2018.html</t>
+          <t>https://www.vino.com/dettaglio/prosecco-asolo-superiore-brilla.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TOR DEL COLLE</t>
+          <t>BRILLA!</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC Riserva 2020 Tor Del Colle</t>
+          <t>Vino Spumante Gassificato Dealcolato Bianco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1141,14 +1141,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.9</v>
+        <v>20.2</v>
       </c>
       <c r="F17" t="n">
-        <v>9.4</v>
+        <v>19.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-abruzzo-doc-riserva-tor-del-colle-2020.html</t>
+          <t>https://www.vino.com/dettaglio/vino-spumante-gassificato-dealcolato-bianco-brilla.html</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prosecco  DOC Extra Dry Brilla!</t>
+          <t>Pinot Grigio delle Venezie DOC Rosé 2023 Brilla!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/prosecco-doc-brilla.html</t>
+          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-rose-brilla-2023.html</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prosecco Superiore di Asolo DOCG Brut Brilla!</t>
+          <t>Prosecco DOC Extra Dry Brilla!</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1223,14 +1223,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,75 L</t>
+          <t>Magnum 1,5 L</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12.4</v>
+        <v>19.9</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4</v>
+        <v>19.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/prosecco-asolo-superiore-brilla.html</t>
+          <t>https://www.vino.com/dettaglio/asolo-prosecco-superiore-docg-brut-magnum-brilla.html</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vino Spumante Gassificato Dealcolato Bianco</t>
+          <t>Pinot Grigio delle Venezie DOC 2023 Brilla!</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1270,14 +1270,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20.2</v>
+        <v>12.8</v>
       </c>
       <c r="F20" t="n">
-        <v>19.2</v>
+        <v>12.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/vino-spumante-gassificato-dealcolato-bianco-brilla.html</t>
+          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-brilla-2023.html</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pinot Grigio delle Venezie DOC Rosé 2023 Brilla!</t>
+          <t>Prosecco DOC Extra Dry Rosé Millesimato 2024 Brilla!</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="F21" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1330,36 +1330,36 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-rose-brilla-2023.html</t>
+          <t>https://www.vino.com/dettaglio/prosecco-doc-brut-rose-brilla-2024.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRILLA!</t>
+          <t>BORGO DEL MANDORLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Prosecco DOC Extra Dry Brilla!</t>
+          <t>Puglia IGT Rosso Appassimento 2025 Borgo del Mandorlo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Magnum 1,5 L</t>
+          <t>0,75 L</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>19.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1373,24 +1373,24 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/asolo-prosecco-superiore-docg-brut-magnum-brilla.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-rosso-appassimento-borgo-del-mandorlo-2025.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRILLA!</t>
+          <t>BORGO DEL MANDORLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pinot Grigio delle Venezie DOC 2023 Brilla!</t>
+          <t>Primitivo di Manduria DOC 2022 Borgo del Mandorlo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F23" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1416,24 +1416,24 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-brilla-2023.html</t>
+          <t>https://www.vino.com/dettaglio/primitivo-di-manduria-doc-borgo-del-mandorlo-2022.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BRILLA!</t>
+          <t>BORGO DEL MANDORLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Prosecco DOC Extra Dry Rosé Millesimato 2024 Brilla!</t>
+          <t>Primitivo di Manduria DOC Riserva 2021 Borgo del Mandorlo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1442,14 +1442,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.6</v>
+        <v>14.1</v>
       </c>
       <c r="F24" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/prosecco-doc-brut-rose-brilla-2024.html</t>
+          <t>https://www.vino.com/dettaglio/primitivo-di-manduria-doc-riserva-borgo-del-mandorlo-2021.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BORGO DEL MANDORLO</t>
+          <t>VELARINO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Puglia IGT Rosso Appassimento 2025 Borgo del Mandorlo</t>
+          <t>Salento IGT Susumaniello 2024 Velarino</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1485,14 +1485,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="F25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1502,24 +1502,24 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-rosso-appassimento-borgo-del-mandorlo-2025.html</t>
+          <t>https://www.vino.com/dettaglio/salento-igt-susumaniello-velarino-2024.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BORGO DEL MANDORLO</t>
+          <t>VELARINO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primitivo di Manduria DOC 2022 Borgo del Mandorlo</t>
+          <t>Puglia IGT Nero di Troia 2024 Velarino</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1528,14 +1528,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="F26" t="n">
-        <v>12.3</v>
+        <v>10.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1545,24 +1545,24 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/primitivo-di-manduria-doc-borgo-del-mandorlo-2022.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-nero-di-troia-velarino-2024.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BORGO DEL MANDORLO</t>
+          <t>VELARINO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Primitivo di Manduria DOC Riserva 2021 Borgo del Mandorlo</t>
+          <t>Salento IGT Malvasia Nera 2023 Velarino</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1571,14 +1571,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14.1</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="n">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/primitivo-di-manduria-doc-riserva-borgo-del-mandorlo-2021.html</t>
+          <t>https://www.vino.com/dettaglio/salento-igt-malvasia-nera-velarino-2023.html</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salento IGT Susumaniello 2024 Velarino</t>
+          <t>Puglia IGT Vermentino 2024 Velarino</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1614,14 +1614,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10.6</v>
+        <v>7.2</v>
       </c>
       <c r="F28" t="n">
-        <v>10.1</v>
+        <v>7.2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1631,19 +1631,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/salento-igt-susumaniello-velarino-2024.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-igt-vermentino-velarino-2024.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VELARINO</t>
+          <t>BOTTER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Puglia IGT Nero di Troia 2024 Velarino</t>
+          <t>Delle Venezie DOC Pinot Grigio 2024 Botter</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1657,14 +1657,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="F29" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-nero-di-troia-velarino-2024.html</t>
+          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-velina-botter-2024.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VELARINO</t>
+          <t>BOTTER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salento IGT Malvasia Nera 2023 Velarino</t>
+          <t>Prosecco Superiore di Asolo DOCG Botter</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1700,14 +1700,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/salento-igt-malvasia-nera-velarino-2023.html</t>
+          <t>https://www.vino.com/dettaglio/prosecco-superiore-asolo-docg-botter.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VELARINO</t>
+          <t>BOTTER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Puglia IGT Vermentino 2024 Velarino</t>
+          <t>Puglia IGT Rosso Appassimento 2024 Botter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="F31" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-igt-vermentino-velarino-2024.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-primitivo-appassimento-velina-botter-2024.html</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Delle Venezie DOC Pinot Grigio 2024 Botter</t>
+          <t>Puglia IGT Primitivo 2024 Botter</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1786,14 +1786,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.1</v>
+        <v>7.4</v>
       </c>
       <c r="F32" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/delle-venezie-doc-pinot-grigio-velina-botter-2024.html</t>
+          <t>https://www.vino.com/dettaglio/puglia-primitivo-velina-uccellini-2024.html</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Puglia IGT Rosso Appassimento 2024 Botter</t>
+          <t>Valdobbiadene Prosecco Superiore DOCG Botter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1829,14 +1829,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10.4</v>
+        <v>12.9</v>
       </c>
       <c r="F33" t="n">
-        <v>10.4</v>
+        <v>12.3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1846,24 +1846,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-primitivo-appassimento-velina-botter-2024.html</t>
+          <t>https://www.vino.com/dettaglio/valdobbiadene-prosecco-superiore-docg-botter.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BOTTER</t>
+          <t>LA DI MOTTE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Prosecco Superiore di Asolo DOCG Botter</t>
+          <t>Friuli DOC Grave Pinot Grigio 2023 La di Motte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1872,14 +1872,14 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
       <c r="F34" t="n">
-        <v>10.8</v>
+        <v>12.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1889,24 +1889,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/prosecco-superiore-asolo-docg-botter.html</t>
+          <t>https://www.vino.com/dettaglio/friuli-doc-grave-pinot-grigio-la-di-motte-2023.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BOTTER</t>
+          <t>LA DI MOTTE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Puglia IGT Primitivo 2024 Botter</t>
+          <t>Trevenezie IGT Pinot Nero 2022 La di Motte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>7.4</v>
+        <v>15.1</v>
       </c>
       <c r="F35" t="n">
-        <v>7.4</v>
+        <v>15.1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1932,24 +1932,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/puglia-primitivo-velina-uccellini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/trevenezie-igt-pinot-nero-la-di-motte-2022.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BOTTER</t>
+          <t>LA DI MOTTE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Valdobbiadene Prosecco Superiore DOCG Botter</t>
+          <t>Trevenezie IGT Rosato 2022 La di Motte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12.9</v>
+        <v>14.9</v>
       </c>
       <c r="F36" t="n">
-        <v>12.3</v>
+        <v>14.2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/valdobbiadene-prosecco-superiore-docg-botter.html</t>
+          <t>https://www.vino.com/dettaglio/trevenezie-igt-rosato-la-di-motte-2022.html</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Friuli DOC Grave Pinot Grigio 2023 La di Motte</t>
+          <t>Friuli DOC Grave Sauvignon 2022 La di Motte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2001,14 +2001,14 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>13.6</v>
+        <v>16.5</v>
       </c>
       <c r="F37" t="n">
-        <v>12.9</v>
+        <v>15.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/friuli-doc-grave-pinot-grigio-la-di-motte-2023.html</t>
+          <t>https://www.vino.com/dettaglio/friuli-doc-grave-sauvignon-la-di-motte-2022.html</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Trevenezie IGT Pinot Nero 2022 La di Motte</t>
+          <t>Friuli DOC Refosco dal Peduncolo Rosso 2022 La di Motte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="F38" t="n">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2061,24 +2061,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/trevenezie-igt-pinot-nero-la-di-motte-2022.html</t>
+          <t>https://www.vino.com/dettaglio/friuli-doc-refosco-dal-peduncolo-rosso-la-di-motte-2022.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LA DI MOTTE</t>
+          <t>LAPILLI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trevenezie IGT Rosato 2022 La di Motte</t>
+          <t>Fiano Beneventano IGT 2023 Lapilli</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="F39" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2104,24 +2104,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/trevenezie-igt-rosato-la-di-motte-2022.html</t>
+          <t>https://www.vino.com/dettaglio/fiano-beneventano-igt-lapilli-2023.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LA DI MOTTE</t>
+          <t>LAPILLI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Friuli DOC Grave Sauvignon 2022 La di Motte</t>
+          <t>Aglianico Beneventano IGT 2023 Lapilli</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2130,14 +2130,14 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="F40" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2147,24 +2147,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/friuli-doc-grave-sauvignon-la-di-motte-2022.html</t>
+          <t>https://www.vino.com/dettaglio/benevento-igt-aglianico-lapilli-2023.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LA DI MOTTE</t>
+          <t>LAPILLI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Friuli DOC Refosco dal Peduncolo Rosso 2022 La di Motte</t>
+          <t>Greco di Tufo DOCG 2023 Lapilli</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>13</v>
+        <v>18.6</v>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>18.6</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/friuli-doc-refosco-dal-peduncolo-rosso-la-di-motte-2022.html</t>
+          <t>https://www.vino.com/dettaglio/greco-di-tufo-docg-lapilli-2023.html</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fiano Beneventano IGT 2023 Lapilli</t>
+          <t>Benevento IGT Falanghina 2023 Lapilli</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2233,19 +2233,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/fiano-beneventano-igt-lapilli-2023.html</t>
+          <t>https://www.vino.com/dettaglio/benevento-igt-falanghina-lapilli-2023.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LAPILLI</t>
+          <t>ZACCAGNINI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aglianico Beneventano IGT 2023 Lapilli</t>
+          <t>Montepulciano d'Abruzzo DOC Il Tralcetto 2023 Zaccagnini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>16.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>16.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2276,24 +2276,24 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/benevento-igt-aglianico-lapilli-2023.html</t>
+          <t>https://www.vino.com/dettaglio/montepulciano-d-abruzzo-doc-il-tralcetto-zaccagnini-2023.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAPILLI</t>
+          <t>ZACCAGNINI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Greco di Tufo DOCG 2023 Lapilli</t>
+          <t>Montepulciano d'Abruzzo DOC Riserva Il Tralcetto 2021 Zaccagnini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2302,14 +2302,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.6</v>
+        <v>13.2</v>
       </c>
       <c r="F44" t="n">
-        <v>18.6</v>
+        <v>12.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2319,36 +2319,36 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/greco-di-tufo-docg-lapilli-2023.html</t>
+          <t>https://www.vino.com/dettaglio/montepulciano-dabruzzo-doc-riserva-il-tralcetto-zaccagnini-2021.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LAPILLI</t>
+          <t>ZACCAGNINI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Benevento IGT Falanghina 2023 Lapilli</t>
+          <t>Terre di Chieti IGT Pecorino La mia Pecora is Green Zaccagnini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0,75 L</t>
+          <t>3 L, Bag in Box</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="F45" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/benevento-igt-falanghina-lapilli-2023.html</t>
+          <t>https://www.vino.com/dettaglio/terre-di-chieti-igt-pecorino-la-mia-pecora-is-green-bag-in-box-zaccagnini.html</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC Il Tralcetto 2023 Zaccagnini</t>
+          <t>Montepulciano d'Abruzzo DOC La mia Pecora is Red 2023 Zaccagnini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2384,14 +2384,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0,75 L</t>
+          <t>3 L, Bag in Box</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9.199999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="F46" t="n">
-        <v>9.199999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-d-abruzzo-doc-il-tralcetto-zaccagnini-2023.html</t>
+          <t>https://www.vino.com/dettaglio/montepulciano-dabruzzo-doc-la-mia-pecora-is-red-zaccagnini-2023.html</t>
         </is>
       </c>
     </row>
@@ -2417,24 +2417,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC Il Tralcetto 2023 Zaccagnini, 6 bottiglie da 0,75 ℓ</t>
+          <t>Cerasuolo d'Abruzzo DOC La mia Pecora is Pink 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0,75 L</t>
+          <t>3 L, Bag in Box</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>55.2</v>
+        <v>14.9</v>
       </c>
       <c r="F47" t="n">
-        <v>55.2</v>
+        <v>14.9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-d-abruzzo-doc-il-tralcetto-zaccagnini-2023_v.html</t>
+          <t>https://www.vino.com/dettaglio/cerasuolo-dabruzzo-doc-la-mia-pecora-is-pink-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC Riserva Il Tralcetto 2021 Zaccagnini</t>
+          <t>Trebbiano d'Abruzzo DOC San Clemente 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2474,14 +2474,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13.2</v>
+        <v>18.6</v>
       </c>
       <c r="F48" t="n">
-        <v>12.5</v>
+        <v>18.6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-dabruzzo-doc-riserva-il-tralcetto-zaccagnini-2021.html</t>
+          <t>https://www.vino.com/dettaglio/trebbiano-dabruzzo-doc-san-clemente-bianco-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trebbiano d'Abruzzo DOC San Clemente 2024 Zaccagnini</t>
+          <t>Abruzzo Pecorino DOC Il Tralcetto 2025 Zaccagnini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2517,14 +2517,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>20.7</v>
+        <v>9.4</v>
       </c>
       <c r="F49" t="n">
-        <v>19.7</v>
+        <v>9.4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/trebbiano-dabruzzo-doc-san-clemente-bianco-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/abruzzo-pecorino-doc-il-tralcetto-zaccagnini-2025.html</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Terre di Chieti IGT Pecorino La mia Pecora is Green Zaccagnini</t>
+          <t>Trebbiano d'Abruzzo DOC San Clemente 2023 Zaccagnini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3 L, Bag in Box</t>
+          <t>0,75 L</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="F50" t="n">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-di-chieti-igt-pecorino-la-mia-pecora-is-green-bag-in-box-zaccagnini.html</t>
+          <t>https://www.vino.com/dettaglio/trebbiano-dabruzzo-doc-san-clemente-bianco-zaccagnini-2023.html</t>
         </is>
       </c>
     </row>
@@ -2589,24 +2589,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC La mia Pecora is Red 2023 Zaccagnini</t>
+          <t>Tralcetto Vino Dealcolato Bianco Zaccagnini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3 L, Bag in Box</t>
+          <t>0,75 L</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-dabruzzo-doc-la-mia-pecora-is-red-zaccagnini-2023.html</t>
+          <t>https://www.vino.com/dettaglio/tralcetto-vino-dealcolato-bianco-zaccagnini.html</t>
         </is>
       </c>
     </row>
@@ -2632,24 +2632,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cerasuolo d'Abruzzo DOC La mia Pecora is Pink 2024 Zaccagnini</t>
+          <t>Tralcetto Vino Dealcolato Rosso Zaccagnini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3 L, Bag in Box</t>
+          <t>0,75 L</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="F52" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/cerasuolo-dabruzzo-doc-la-mia-pecora-is-pink-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/tralcetto-vino-dealcolato-rosso-zaccagnini.html</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trebbiano d'Abruzzo DOC San Clemente 2023 Zaccagnini</t>
+          <t>Cerasuolo d'Abruzzo DOC Chronicon 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="F53" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/trebbiano-dabruzzo-doc-san-clemente-bianco-zaccagnini-2023.html</t>
+          <t>https://www.vino.com/dettaglio/cerasuolo-abruzzo-chronicon-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Abruzzo Pecorino DOC Il Tralcetto 2025 Zaccagnini</t>
+          <t>Trebbiano d'Abruzzo DOC Il Bianco di Ciccio 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="F54" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/abruzzo-pecorino-doc-il-tralcetto-zaccagnini-2025.html</t>
+          <t>https://www.vino.com/dettaglio/abruzzo-doc-il-bianco-di-ciccio-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tralcetto Vino Dealcolato Bianco Zaccagnini</t>
+          <t>Montepulciano d'Abruzzo DOC Chronicon 2022 Zaccagnini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="F56" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/tralcetto-vino-dealcolato-bianco-zaccagnini.html</t>
+          <t>https://www.vino.com/dettaglio/montepulciano-d-abruzzo-doc-chronicon-zaccagnini-2022.html</t>
         </is>
       </c>
     </row>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tralcetto Vino Dealcolato Rosso Zaccagnini</t>
+          <t>Abruzzo Pecorino DOC Chronicon 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="F57" t="n">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/tralcetto-vino-dealcolato-rosso-zaccagnini.html</t>
+          <t>https://www.vino.com/dettaglio/abruzzo-pecorino-doc-chronicon-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cerasuolo d'Abruzzo DOC Chronicon 2024 Zaccagnini</t>
+          <t>Cerasuolo d'Abruzzo DOC Il Tralcetto 2024 Zaccagnini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="F58" t="n">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2921,24 +2921,24 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/cerasuolo-abruzzo-chronicon-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/cerasuolo-d-abruzzo-doc-il-tralcetto-zaccagnini-2024.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ZACCAGNINI</t>
+          <t>BARONE MONTALTO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trebbiano d'Abruzzo DOC Il Bianco di Ciccio 2024 Zaccagnini</t>
+          <t>Sicilia DOC Rosso Ammasso 2021 Barone Montalto</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>23.6</v>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>23.6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2964,24 +2964,24 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/abruzzo-doc-il-bianco-di-ciccio-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/sicilia-doc-rosso-ammasso-barone-montalto-2021.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ZACCAGNINI</t>
+          <t>BARONE MONTALTO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Montepulciano d'Abruzzo DOC Chronicon 2022 Zaccagnini</t>
+          <t>Etna DOC Rosso Fumu 2021 Barone Montalto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2990,14 +2990,14 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>11.2</v>
+        <v>21.6</v>
       </c>
       <c r="F60" t="n">
-        <v>11.2</v>
+        <v>20.5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3007,24 +3007,24 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/montepulciano-d-abruzzo-doc-chronicon-zaccagnini-2022.html</t>
+          <t>https://www.vino.com/dettaglio/etna-doc-rosso-fumu-barone-montalto-2021.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZACCAGNINI</t>
+          <t>BARONE MONTALTO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abruzzo Pecorino DOC Chronicon 2024 Zaccagnini</t>
+          <t>Etna DOC Bianco Fumu 2023 Barone Montalto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3033,14 +3033,14 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10.6</v>
+        <v>21.6</v>
       </c>
       <c r="F61" t="n">
-        <v>10.6</v>
+        <v>20.5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3050,24 +3050,24 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/abruzzo-pecorino-doc-chronicon-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/etna-doc-bianco-fumu-barone-montalto-2023.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZACCAGNINI</t>
+          <t>BARONE MONTALTO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cerasuolo d'Abruzzo DOC Il Tralcetto 2024 Zaccagnini</t>
+          <t>Terre Siciliane IGP Rosato Passivento 2021 Barone Montalto</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>9.1</v>
+        <v>15.8</v>
       </c>
       <c r="F62" t="n">
-        <v>9.1</v>
+        <v>15.8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/cerasuolo-d-abruzzo-doc-il-tralcetto-zaccagnini-2024.html</t>
+          <t>https://www.vino.com/dettaglio/terre-siciliane-igp-rosato-passivento-barone-montalto-2021.html</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sicilia DOC Rosso Ammasso 2021 Barone Montalto</t>
+          <t>Terre Siciliane IGP Bianco Passivento 2024 Barone Montalto</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>23.6</v>
+        <v>15.8</v>
       </c>
       <c r="F63" t="n">
-        <v>23.6</v>
+        <v>15.8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/sicilia-doc-rosso-ammasso-barone-montalto-2021.html</t>
+          <t>https://www.vino.com/dettaglio/terre-siciliane-bianco-passivento-barone-montalto-2024.html</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Etna DOC Rosso Fumu 2021 Barone Montalto</t>
+          <t>Terre Siciliane IGT Syrah Due Mondi 2023 Barone Montalto</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3162,14 +3162,14 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>21.6</v>
+        <v>12.4</v>
       </c>
       <c r="F64" t="n">
-        <v>20.5</v>
+        <v>12.4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/etna-doc-rosso-fumu-barone-montalto-2021.html</t>
+          <t>https://www.vino.com/dettaglio/terre-siciliane-igp-syrah-acquarello-barone-montalto-2023.html</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Etna DOC Bianco Fumu 2023 Barone Montalto</t>
+          <t>Terre Siciliane IGP Rosso Passivento 2024 Barone Montalto</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3205,14 +3205,14 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>21.6</v>
+        <v>16.1</v>
       </c>
       <c r="F65" t="n">
-        <v>20.5</v>
+        <v>15.3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3222,24 +3222,24 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/etna-doc-bianco-fumu-barone-montalto-2023.html</t>
+          <t>https://www.vino.com/dettaglio/terre-siciliane-igt-passivento-barone-montalto-2024.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BARONE MONTALTO</t>
+          <t>RICOSSA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Terre Siciliane IGP Rosato Passivento 2021 Barone Montalto</t>
+          <t>Barbaresco DOCG 2020 Ricossa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3248,14 +3248,14 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>15.8</v>
+        <v>25.3</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>25.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3265,24 +3265,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-siciliane-igp-rosato-passivento-barone-montalto-2021.html</t>
+          <t>https://www.vino.com/dettaglio/barbaresco-docg-ricossa-2020.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BARONE MONTALTO</t>
+          <t>RICOSSA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Terre Siciliane IGP Bianco Passivento 2024 Barone Montalto</t>
+          <t>Barolo DOCG Riserva 2017 Ricossa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>15.8</v>
+        <v>40.4</v>
       </c>
       <c r="F67" t="n">
-        <v>15.8</v>
+        <v>40.4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3308,19 +3308,19 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-siciliane-bianco-passivento-barone-montalto-2024.html</t>
+          <t>https://www.vino.com/dettaglio/barolo-docg-riserva-ricossa-2017.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BARONE MONTALTO</t>
+          <t>RICOSSA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Terre Siciliane IGT Syrah Due Mondi 2023 Barone Montalto</t>
+          <t>Piemonte DOC Barbera Appassimento 2023 Ricossa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="F68" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3351,24 +3351,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-siciliane-igp-syrah-acquarello-barone-montalto-2023.html</t>
+          <t>https://www.vino.com/dettaglio/piemonte-doc-barbera-appassimento-ricossa-2023.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BARONE MONTALTO</t>
+          <t>RICOSSA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Terre Siciliane IGP Rosso Passivento 2024 Barone Montalto</t>
+          <t>Barbera d'Asti Superiore DOCG 2019 Ricossa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3377,14 +3377,14 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>16.1</v>
+        <v>14.9</v>
       </c>
       <c r="F69" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/terre-siciliane-igt-passivento-barone-montalto-2024.html</t>
+          <t>https://www.vino.com/dettaglio/barbera-asti-superiore-docg-ricossa-2019.html</t>
         </is>
       </c>
     </row>
@@ -3406,12 +3406,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Barbaresco DOCG 2020 Ricossa</t>
+          <t>Langhe DOP Nebbiolo 2024 Ricossa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>25.3</v>
+        <v>12.9</v>
       </c>
       <c r="F70" t="n">
-        <v>25.3</v>
+        <v>12.9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3437,24 +3437,24 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/barbaresco-docg-ricossa-2020.html</t>
+          <t>https://www.vino.com/dettaglio/langhe-dop-nebbiolo-ricossa-2024.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RICOSSA</t>
+          <t>CUVAGE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Barolo DOCG Riserva 2017 Ricossa</t>
+          <t>Piemonte DOC Brut Blanc de Blancs Cuvage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3463,14 +3463,14 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>40.4</v>
+        <v>20.7</v>
       </c>
       <c r="F71" t="n">
-        <v>40.4</v>
+        <v>19.7</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3480,24 +3480,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/barolo-docg-riserva-ricossa-2017.html</t>
+          <t>https://www.vino.com/dettaglio/piemonte-doc-blanc-de-blancs-brut-cuvage.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RICOSSA</t>
+          <t>CUVAGE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Piemonte DOC Barbera Appassimento 2023 Ricossa</t>
+          <t>Nebbiolo d'Alba DOC Rosé Brut 2020 Cuvage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>14.4</v>
+        <v>23.8</v>
       </c>
       <c r="F72" t="n">
-        <v>14.4</v>
+        <v>23.8</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3523,24 +3523,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.vino.com/dettaglio/piemonte-doc-barbera-appassimento-ricossa-2023.html</t>
+          <t>https://www.vino.com/dettaglio/nebbiolo-alba-doc-rose-brut-cuvage-2020.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RICOSSA</t>
+          <t>CUVAGE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Barbera d'Asti Superiore DOCG 2019 Ricossa</t>
+          <t>Vino Spumante di Qualità Metodo Classico Pas Dosé Cuvage</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>14.9</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
-        <v>14.9</v>
+        <v>25</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3565,178 +3565,6 @@
         </is>
       </c>
       <c r="I73" t="inlineStr">
-        <is>
-          <t>https://www.vino.com/dettaglio/barbera-asti-superiore-docg-ricossa-2019.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>RICOSSA</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Langhe DOP Nebbiolo 2024 Ricossa</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>0,75 L</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F74" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>https://www.vino.com/dettaglio/langhe-dop-nebbiolo-ricossa-2024.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CUVAGE</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Piemonte DOC Brut Blanc de Blancs Cuvage</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>0,75 L</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F75" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>https://www.vino.com/dettaglio/piemonte-doc-blanc-de-blancs-brut-cuvage.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>CUVAGE</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Nebbiolo d'Alba DOC Rosé Brut 2020 Cuvage</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>0,75 L</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="F76" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>https://www.vino.com/dettaglio/nebbiolo-alba-doc-rose-brut-cuvage-2020.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CUVAGE</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Vino Spumante di Qualità Metodo Classico Pas Dosé Cuvage</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>0,75 L</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>25</v>
-      </c>
-      <c r="F77" t="n">
-        <v>25</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
         <is>
           <t>https://www.vino.com/dettaglio/vino-spumante-di-qualita-cuvage-de-cuvage-pas-dose-cuvage.html</t>
         </is>
